--- a/docs/data/umea.xlsx
+++ b/docs/data/umea.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jomjom03/Documents/GitHub/pay-calculator/docs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EB08717-39A8-0640-8CCA-87F53053845C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F1B9D0-7B04-9644-9CC1-F0217EAA83A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -727,7 +727,7 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>47700</v>
